--- a/data/trans_orig/IP1007-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1007-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101701</t>
+          <t>101748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>199652</t>
+          <t>199245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82731</t>
+          <t>83100</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170058</t>
+          <t>170106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197254</t>
+          <t>197706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399791</t>
+          <t>399231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101182</t>
+          <t>101252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122357</t>
+          <t>123003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225864</t>
+          <t>225645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230798</t>
+          <t>230794</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69144</t>
+          <t>69532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144504</t>
+          <t>143705</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634151</t>
+          <t>634309</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638332</t>
+          <t>638856</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>678385</t>
+          <t>677802</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314799</t>
+          <t>1314670</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1321618</t>
+          <t>1321486</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89529</t>
+          <t>89865</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185974</t>
+          <t>185982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145514</t>
+          <t>145512</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135372</t>
+          <t>136347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>283352</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>568</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>669188</t>
+          <t>668793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>710036</t>
+          <t>709900</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1381688</t>
+          <t>1381646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1387017</t>
+          <t>1387014</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96358</t>
+          <t>97012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179017</t>
+          <t>180074</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>217833</t>
+          <t>217782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>429748</t>
+          <t>428590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138684</t>
+          <t>138428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275477</t>
+          <t>274616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>665916</t>
+          <t>665725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>703812</t>
+          <t>704160</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1373256</t>
+          <t>1373229</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1380075</t>
+          <t>1380547</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1007-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1007-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2604</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2643</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2815</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2653</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>103828</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>101748</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>101709</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,47%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>298</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>199245</t>
+          <t>199083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2870</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85328</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82711</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85328</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>83100</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170106</t>
+          <t>170259</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3027</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3625</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3010</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3576</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200135</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>197706</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>197108</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>606</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399231</t>
+          <t>399797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>616</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2868</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3126</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4286</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>125863</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122319</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>103504</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>101252</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>100994</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,41%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>125863</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123003</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>345</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225645</t>
+          <t>225928</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230794</t>
+          <t>230797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,107 +2437,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2860</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3575</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3557</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2550,72 +2550,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>71745</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>68489</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,61%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>71745</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>69532</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143705</t>
+          <t>143687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2715</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6339</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1738</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4547</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4787</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2715</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6801</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>681888</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>678264</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>683953</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>950</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>637118</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>634309</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>638856</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>634069</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>638335</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,73%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>681888</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>677802</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>683902</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314670</t>
+          <t>1314604</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1321486</t>
+          <t>1321502</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3470,47 +3470,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,107 +3700,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>568</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2864</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2893</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2858</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3813,74 +3813,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92161</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>89865</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>89836</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,39%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>273</t>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185982</t>
+          <t>185950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4156,47 +4156,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4499,47 +4499,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4734,102 +4734,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3441</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3657</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4923</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3487</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1583</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5651</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4842,74 +4842,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139147</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136393</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>148273</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>145512</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>144246</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,4%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139147</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136347</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>406</t>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283352</t>
+          <t>283436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5185,47 +5185,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3458</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1464</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5288</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4962</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3601</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>712814</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>710043</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>672617</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>668793</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>669119</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,78%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>712814</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>709900</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1988</t>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1381646</t>
+          <t>1382031</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,107 +5992,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>692</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>692</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3478</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99105</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>96071</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99105</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>97012</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180074</t>
+          <t>179409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6448,47 +6448,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6791,47 +6791,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,107 +7021,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1163</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5795</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5780</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5841</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -7134,74 +7134,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>222414</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>217782</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>218249</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,62%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>641</t>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>428590</t>
+          <t>428651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,107 +7364,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1262</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4660</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4052</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4666</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>141826</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>139211</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>141826</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>138428</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274616</t>
+          <t>275230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5443</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1163</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5777</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5813</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5577</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -8163,74 +8163,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>707784</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>704294</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>709109</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1012</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>670339</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>665725</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>665689</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,83%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>707784</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>704160</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>709112</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1373229</t>
+          <t>1373127</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1380547</t>
+          <t>1380546</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
